--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/24,08,26 Останкино КИ и ЗПФ/дв 24,08,26 млрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/24,08,26 Останкино КИ и ЗПФ/дв 24,08,26 млрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\24,08,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4DCC93-0A98-41E6-8A88-C5DA7BF44E5A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828FB471-633E-481E-AD8F-2E8BB831C924}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AF$112</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1058,7 +1058,8 @@
     <col min="21" max="30" width="6" customWidth="1"/>
     <col min="31" max="31" width="44.140625" customWidth="1"/>
     <col min="32" max="32" width="7" customWidth="1"/>
-    <col min="33" max="49" width="3" customWidth="1"/>
+    <col min="33" max="33" width="7.5703125" customWidth="1"/>
+    <col min="34" max="49" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
@@ -1451,7 +1452,10 @@
         <f>SUM(AF6:AF499)</f>
         <v>5058.1499999999996</v>
       </c>
-      <c r="AG5" s="1"/>
+      <c r="AG5" s="4">
+        <f>SUM(AG6:AG499)</f>
+        <v>917.44640000000015</v>
+      </c>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
@@ -1565,7 +1569,10 @@
         <f>G6*R6</f>
         <v>91.600000000000009</v>
       </c>
-      <c r="AG6" s="1"/>
+      <c r="AG6" s="1">
+        <f>P6*G6</f>
+        <v>15.12</v>
+      </c>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
@@ -1678,7 +1685,10 @@
         <f t="shared" ref="AF7:AF70" si="7">G7*R7</f>
         <v>0</v>
       </c>
-      <c r="AG7" s="1"/>
+      <c r="AG7" s="1">
+        <f t="shared" ref="AG7:AG70" si="8">P7*G7</f>
+        <v>-8.0800000000000011E-2</v>
+      </c>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
@@ -1791,7 +1801,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG8" s="1"/>
+      <c r="AG8" s="1">
+        <f t="shared" si="8"/>
+        <v>6.05</v>
+      </c>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
@@ -1855,7 +1868,7 @@
         <v>35.8078</v>
       </c>
       <c r="Q9" s="5">
-        <f t="shared" ref="Q9:Q17" si="8">15*P9-O9-F9</f>
+        <f t="shared" ref="Q9:Q17" si="9">15*P9-O9-F9</f>
         <v>270.59399999999994</v>
       </c>
       <c r="R9" s="5">
@@ -1905,7 +1918,10 @@
         <f t="shared" si="7"/>
         <v>271</v>
       </c>
-      <c r="AG9" s="1"/>
+      <c r="AG9" s="1">
+        <f t="shared" si="8"/>
+        <v>35.8078</v>
+      </c>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
@@ -2018,7 +2034,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG10" s="1"/>
+      <c r="AG10" s="1">
+        <f t="shared" si="8"/>
+        <v>1.9966000000000002</v>
+      </c>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
@@ -2130,7 +2149,10 @@
         <f t="shared" si="7"/>
         <v>49</v>
       </c>
-      <c r="AG11" s="1"/>
+      <c r="AG11" s="1">
+        <f t="shared" si="8"/>
+        <v>6.1752000000000002</v>
+      </c>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
@@ -2243,7 +2265,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG12" s="1"/>
+      <c r="AG12" s="1">
+        <f t="shared" si="8"/>
+        <v>13.480600000000001</v>
+      </c>
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
@@ -2307,7 +2332,7 @@
         <v>24</v>
       </c>
       <c r="Q13" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
       <c r="R13" s="5">
@@ -2359,7 +2384,10 @@
         <f t="shared" si="7"/>
         <v>1.75</v>
       </c>
-      <c r="AG13" s="1"/>
+      <c r="AG13" s="1">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
@@ -2466,7 +2494,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG14" s="1"/>
+      <c r="AG14" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
@@ -2530,7 +2561,7 @@
         <v>42.6</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>136</v>
       </c>
       <c r="R15" s="5">
@@ -2582,7 +2613,10 @@
         <f t="shared" si="7"/>
         <v>34</v>
       </c>
-      <c r="AG15" s="1"/>
+      <c r="AG15" s="1">
+        <f t="shared" si="8"/>
+        <v>10.65</v>
+      </c>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
@@ -2691,7 +2725,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG16" s="1"/>
+      <c r="AG16" s="1">
+        <f t="shared" si="8"/>
+        <v>5.2</v>
+      </c>
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
@@ -2755,7 +2792,7 @@
         <v>32.3752</v>
       </c>
       <c r="Q17" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>186.14399999999998</v>
       </c>
       <c r="R17" s="5">
@@ -2805,7 +2842,10 @@
         <f t="shared" si="7"/>
         <v>186</v>
       </c>
-      <c r="AG17" s="1"/>
+      <c r="AG17" s="1">
+        <f t="shared" si="8"/>
+        <v>32.3752</v>
+      </c>
       <c r="AH17" s="1"/>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
@@ -2910,7 +2950,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG18" s="1"/>
+      <c r="AG18" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH18" s="1"/>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
@@ -3023,7 +3066,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG19" s="1"/>
+      <c r="AG19" s="1">
+        <f t="shared" si="8"/>
+        <v>3.2415999999999996</v>
+      </c>
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
@@ -3137,7 +3183,10 @@
         <f t="shared" si="7"/>
         <v>130.80000000000001</v>
       </c>
-      <c r="AG20" s="1"/>
+      <c r="AG20" s="1">
+        <f t="shared" si="8"/>
+        <v>17.36</v>
+      </c>
       <c r="AH20" s="1"/>
       <c r="AI20" s="1"/>
       <c r="AJ20" s="1"/>
@@ -3248,7 +3297,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG21" s="1"/>
+      <c r="AG21" s="1">
+        <f t="shared" si="8"/>
+        <v>10.878</v>
+      </c>
       <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
@@ -3312,7 +3364,7 @@
         <v>45.4</v>
       </c>
       <c r="Q22" s="5">
-        <f t="shared" ref="Q22:Q23" si="9">15*P22-O22-F22</f>
+        <f t="shared" ref="Q22:Q23" si="10">15*P22-O22-F22</f>
         <v>200</v>
       </c>
       <c r="R22" s="5">
@@ -3364,7 +3416,10 @@
         <f t="shared" si="7"/>
         <v>44</v>
       </c>
-      <c r="AG22" s="1"/>
+      <c r="AG22" s="1">
+        <f t="shared" si="8"/>
+        <v>9.9879999999999995</v>
+      </c>
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
@@ -3428,7 +3483,7 @@
         <v>2.4996</v>
       </c>
       <c r="Q23" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.0459999999999994</v>
       </c>
       <c r="R23" s="5">
@@ -3478,7 +3533,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="AG23" s="1"/>
+      <c r="AG23" s="1">
+        <f t="shared" si="8"/>
+        <v>2.4996</v>
+      </c>
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
@@ -3583,7 +3641,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG24" s="1"/>
+      <c r="AG24" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
@@ -3694,7 +3755,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG25" s="1"/>
+      <c r="AG25" s="1">
+        <f t="shared" si="8"/>
+        <v>9.1290000000000013</v>
+      </c>
       <c r="AH25" s="1"/>
       <c r="AI25" s="1"/>
       <c r="AJ25" s="1"/>
@@ -3758,7 +3822,7 @@
         <v>10</v>
       </c>
       <c r="Q26" s="5">
-        <f t="shared" ref="Q26:Q29" si="10">15*P26-O26-F26</f>
+        <f t="shared" ref="Q26:Q29" si="11">15*P26-O26-F26</f>
         <v>36</v>
       </c>
       <c r="R26" s="5">
@@ -3808,7 +3872,10 @@
         <f t="shared" si="7"/>
         <v>3.2399999999999998</v>
       </c>
-      <c r="AG26" s="1"/>
+      <c r="AG26" s="1">
+        <f t="shared" si="8"/>
+        <v>0.89999999999999991</v>
+      </c>
       <c r="AH26" s="1"/>
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
@@ -3872,7 +3939,7 @@
         <v>11</v>
       </c>
       <c r="Q27" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>26</v>
       </c>
       <c r="R27" s="5">
@@ -3924,7 +3991,10 @@
         <f t="shared" si="7"/>
         <v>2.34</v>
       </c>
-      <c r="AG27" s="1"/>
+      <c r="AG27" s="1">
+        <f t="shared" si="8"/>
+        <v>0.99</v>
+      </c>
       <c r="AH27" s="1"/>
       <c r="AI27" s="1"/>
       <c r="AJ27" s="1"/>
@@ -4038,7 +4108,10 @@
         <f t="shared" si="7"/>
         <v>34.949999999999996</v>
       </c>
-      <c r="AG28" s="1"/>
+      <c r="AG28" s="1">
+        <f t="shared" si="8"/>
+        <v>4.32</v>
+      </c>
       <c r="AH28" s="1"/>
       <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
@@ -4102,7 +4175,7 @@
         <v>59.6554</v>
       </c>
       <c r="Q29" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>383.274</v>
       </c>
       <c r="R29" s="5">
@@ -4152,7 +4225,10 @@
         <f t="shared" si="7"/>
         <v>383</v>
       </c>
-      <c r="AG29" s="1"/>
+      <c r="AG29" s="1">
+        <f t="shared" si="8"/>
+        <v>59.6554</v>
+      </c>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
@@ -4263,7 +4339,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG30" s="1"/>
+      <c r="AG30" s="1">
+        <f t="shared" si="8"/>
+        <v>0.96</v>
+      </c>
       <c r="AH30" s="1"/>
       <c r="AI30" s="1"/>
       <c r="AJ30" s="1"/>
@@ -4377,7 +4456,10 @@
         <f t="shared" si="7"/>
         <v>171.60000000000002</v>
       </c>
-      <c r="AG31" s="1"/>
+      <c r="AG31" s="1">
+        <f t="shared" si="8"/>
+        <v>22</v>
+      </c>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
@@ -4488,7 +4570,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG32" s="1"/>
+      <c r="AG32" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH32" s="1"/>
       <c r="AI32" s="1"/>
       <c r="AJ32" s="1"/>
@@ -4552,7 +4637,7 @@
         <v>40</v>
       </c>
       <c r="Q33" s="5">
-        <f t="shared" ref="Q33" si="11">15*P33-O33-F33</f>
+        <f t="shared" ref="Q33" si="12">15*P33-O33-F33</f>
         <v>154</v>
       </c>
       <c r="R33" s="5">
@@ -4602,7 +4687,10 @@
         <f t="shared" si="7"/>
         <v>61.6</v>
       </c>
-      <c r="AG33" s="1"/>
+      <c r="AG33" s="1">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
@@ -4718,7 +4806,10 @@
         <f t="shared" si="7"/>
         <v>11.1</v>
       </c>
-      <c r="AG34" s="1"/>
+      <c r="AG34" s="1">
+        <f t="shared" si="8"/>
+        <v>1.32</v>
+      </c>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
@@ -4829,7 +4920,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG35" s="1"/>
+      <c r="AG35" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
@@ -4942,7 +5036,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG36" s="1"/>
+      <c r="AG36" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
@@ -5051,7 +5148,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG37" s="1"/>
+      <c r="AG37" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
@@ -5100,7 +5200,7 @@
         <v>157</v>
       </c>
       <c r="L38" s="9">
-        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
         <v>-162</v>
       </c>
       <c r="M38" s="9"/>
@@ -5109,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="P38" s="9">
-        <f t="shared" ref="P38:P69" si="13">E38/5</f>
+        <f t="shared" ref="P38:P69" si="14">E38/5</f>
         <v>-1</v>
       </c>
       <c r="Q38" s="11"/>
@@ -5122,7 +5222,7 @@
         <v>-30</v>
       </c>
       <c r="T38" s="9">
-        <f t="shared" ref="T38:T69" si="14">(F38+O38)/P38</f>
+        <f t="shared" ref="T38:T69" si="15">(F38+O38)/P38</f>
         <v>-30</v>
       </c>
       <c r="U38" s="9">
@@ -5162,7 +5262,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG38" s="1"/>
+      <c r="AG38" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH38" s="1"/>
       <c r="AI38" s="1"/>
       <c r="AJ38" s="1"/>
@@ -5213,7 +5316,7 @@
         <v>47</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-18</v>
       </c>
       <c r="M39" s="1"/>
@@ -5222,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.8</v>
       </c>
       <c r="Q39" s="5">
@@ -5238,7 +5341,7 @@
         <v>11.03448275862069</v>
       </c>
       <c r="T39" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.2758620689655173</v>
       </c>
       <c r="U39" s="1">
@@ -5276,7 +5379,10 @@
         <f t="shared" si="7"/>
         <v>13.5</v>
       </c>
-      <c r="AG39" s="1"/>
+      <c r="AG39" s="1">
+        <f t="shared" si="8"/>
+        <v>1.74</v>
+      </c>
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
@@ -5327,7 +5433,7 @@
         <v>74.900000000000006</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.9460000000000122</v>
       </c>
       <c r="M40" s="1"/>
@@ -5336,11 +5442,11 @@
         <v>0</v>
       </c>
       <c r="P40" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14.590799999999998</v>
       </c>
       <c r="Q40" s="5">
-        <f t="shared" ref="Q40" si="15">15*P40-O40-F40</f>
+        <f t="shared" ref="Q40" si="16">15*P40-O40-F40</f>
         <v>83.876999999999953</v>
       </c>
       <c r="R40" s="5">
@@ -5352,7 +5458,7 @@
         <v>15.008429969569869</v>
       </c>
       <c r="T40" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.2513775803931271</v>
       </c>
       <c r="U40" s="1">
@@ -5390,7 +5496,10 @@
         <f t="shared" si="7"/>
         <v>84</v>
       </c>
-      <c r="AG40" s="1"/>
+      <c r="AG40" s="1">
+        <f t="shared" si="8"/>
+        <v>14.590799999999998</v>
+      </c>
       <c r="AH40" s="1"/>
       <c r="AI40" s="1"/>
       <c r="AJ40" s="1"/>
@@ -5441,7 +5550,7 @@
         <v>50</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.2689999999999984</v>
       </c>
       <c r="M41" s="1"/>
@@ -5450,7 +5559,7 @@
         <v>108</v>
       </c>
       <c r="P41" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.8538</v>
       </c>
       <c r="Q41" s="5"/>
@@ -5463,7 +5572,7 @@
         <v>16.026829313235918</v>
       </c>
       <c r="T41" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>16.026829313235918</v>
       </c>
       <c r="U41" s="1">
@@ -5501,7 +5610,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG41" s="1"/>
+      <c r="AG41" s="1">
+        <f t="shared" si="8"/>
+        <v>10.8538</v>
+      </c>
       <c r="AH41" s="1"/>
       <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
@@ -5552,7 +5664,7 @@
         <v>50</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.6940000000000026</v>
       </c>
       <c r="M42" s="1"/>
@@ -5561,7 +5673,7 @@
         <v>67</v>
       </c>
       <c r="P42" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.5388</v>
       </c>
       <c r="Q42" s="5"/>
@@ -5574,7 +5686,7 @@
         <v>19.414923900254298</v>
       </c>
       <c r="T42" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>19.414923900254298</v>
       </c>
       <c r="U42" s="1">
@@ -5614,7 +5726,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG42" s="1"/>
+      <c r="AG42" s="1">
+        <f t="shared" si="8"/>
+        <v>10.5388</v>
+      </c>
       <c r="AH42" s="1"/>
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
@@ -5665,7 +5780,7 @@
         <v>43</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.0609999999999999</v>
       </c>
       <c r="M43" s="1"/>
@@ -5674,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="P43" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.2121999999999993</v>
       </c>
       <c r="Q43" s="5"/>
@@ -5687,7 +5802,7 @@
         <v>17.716397820281802</v>
       </c>
       <c r="T43" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>17.716397820281802</v>
       </c>
       <c r="U43" s="1">
@@ -5725,7 +5840,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG43" s="1"/>
+      <c r="AG43" s="1">
+        <f t="shared" si="8"/>
+        <v>9.2121999999999993</v>
+      </c>
       <c r="AH43" s="1"/>
       <c r="AI43" s="1"/>
       <c r="AJ43" s="1"/>
@@ -5776,7 +5894,7 @@
         <v>333</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-12</v>
       </c>
       <c r="M44" s="1"/>
@@ -5785,7 +5903,7 @@
         <v>245</v>
       </c>
       <c r="P44" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>64.2</v>
       </c>
       <c r="Q44" s="5">
@@ -5801,7 +5919,7 @@
         <v>11.993769470404985</v>
       </c>
       <c r="T44" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.9719626168224296</v>
       </c>
       <c r="U44" s="1">
@@ -5839,7 +5957,10 @@
         <f t="shared" si="7"/>
         <v>154.5</v>
       </c>
-      <c r="AG44" s="1"/>
+      <c r="AG44" s="1">
+        <f t="shared" si="8"/>
+        <v>19.260000000000002</v>
+      </c>
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
@@ -5878,7 +5999,7 @@
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M45" s="9"/>
@@ -5887,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q45" s="11"/>
@@ -5900,7 +6021,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T45" s="9" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U45" s="9">
@@ -5940,7 +6061,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG45" s="1"/>
+      <c r="AG45" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH45" s="1"/>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
@@ -5991,7 +6115,7 @@
         <v>58.5</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8.5090000000000003</v>
       </c>
       <c r="M46" s="1"/>
@@ -6000,11 +6124,11 @@
         <v>0</v>
       </c>
       <c r="P46" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.4018</v>
       </c>
       <c r="Q46" s="5">
-        <f t="shared" ref="Q46:Q53" si="16">15*P46-O46-F46</f>
+        <f t="shared" ref="Q46:Q53" si="17">15*P46-O46-F46</f>
         <v>92.911999999999992</v>
       </c>
       <c r="R46" s="5">
@@ -6016,7 +6140,7 @@
         <v>15.006566282141206</v>
       </c>
       <c r="T46" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.0671999283678311</v>
       </c>
       <c r="U46" s="1">
@@ -6054,7 +6178,10 @@
         <f t="shared" si="7"/>
         <v>93</v>
       </c>
-      <c r="AG46" s="1"/>
+      <c r="AG46" s="1">
+        <f t="shared" si="8"/>
+        <v>13.4018</v>
+      </c>
       <c r="AH46" s="1"/>
       <c r="AI46" s="1"/>
       <c r="AJ46" s="1"/>
@@ -6105,7 +6232,7 @@
         <v>367</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-25</v>
       </c>
       <c r="M47" s="1"/>
@@ -6114,11 +6241,11 @@
         <v>489</v>
       </c>
       <c r="P47" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>68.400000000000006</v>
       </c>
       <c r="Q47" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>256.8</v>
       </c>
       <c r="R47" s="5">
@@ -6130,7 +6257,7 @@
         <v>15.002923976608187</v>
       </c>
       <c r="T47" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.245614035087719</v>
       </c>
       <c r="U47" s="1">
@@ -6168,7 +6295,10 @@
         <f t="shared" si="7"/>
         <v>89.949999999999989</v>
       </c>
-      <c r="AG47" s="1"/>
+      <c r="AG47" s="1">
+        <f t="shared" si="8"/>
+        <v>23.94</v>
+      </c>
       <c r="AH47" s="1"/>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
@@ -6219,7 +6349,7 @@
         <v>233</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-23</v>
       </c>
       <c r="M48" s="1"/>
@@ -6228,7 +6358,7 @@
         <v>251</v>
       </c>
       <c r="P48" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>42</v>
       </c>
       <c r="Q48" s="5">
@@ -6244,7 +6374,7 @@
         <v>14</v>
       </c>
       <c r="T48" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.0714285714285712</v>
       </c>
       <c r="U48" s="1">
@@ -6282,7 +6412,10 @@
         <f t="shared" si="7"/>
         <v>136.53</v>
       </c>
-      <c r="AG48" s="1"/>
+      <c r="AG48" s="1">
+        <f t="shared" si="8"/>
+        <v>17.22</v>
+      </c>
       <c r="AH48" s="1"/>
       <c r="AI48" s="1"/>
       <c r="AJ48" s="1"/>
@@ -6333,7 +6466,7 @@
         <v>131</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1</v>
       </c>
       <c r="M49" s="1"/>
@@ -6342,7 +6475,7 @@
         <v>295</v>
       </c>
       <c r="P49" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>26</v>
       </c>
       <c r="Q49" s="5"/>
@@ -6355,7 +6488,7 @@
         <v>15.307692307692308</v>
       </c>
       <c r="T49" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.307692307692308</v>
       </c>
       <c r="U49" s="1">
@@ -6393,7 +6526,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG49" s="1"/>
+      <c r="AG49" s="1">
+        <f t="shared" si="8"/>
+        <v>10.66</v>
+      </c>
       <c r="AH49" s="1"/>
       <c r="AI49" s="1"/>
       <c r="AJ49" s="1"/>
@@ -6444,7 +6580,7 @@
         <v>194</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-25</v>
       </c>
       <c r="M50" s="1"/>
@@ -6453,7 +6589,7 @@
         <v>179</v>
       </c>
       <c r="P50" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>33.799999999999997</v>
       </c>
       <c r="Q50" s="5">
@@ -6469,7 +6605,7 @@
         <v>12.988165680473374</v>
       </c>
       <c r="T50" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.4142011834319534</v>
       </c>
       <c r="U50" s="1">
@@ -6507,7 +6643,10 @@
         <f t="shared" si="7"/>
         <v>92.16</v>
       </c>
-      <c r="AG50" s="1"/>
+      <c r="AG50" s="1">
+        <f t="shared" si="8"/>
+        <v>12.167999999999999</v>
+      </c>
       <c r="AH50" s="1"/>
       <c r="AI50" s="1"/>
       <c r="AJ50" s="1"/>
@@ -6554,7 +6693,7 @@
         <v>21</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-15</v>
       </c>
       <c r="M51" s="1"/>
@@ -6563,7 +6702,7 @@
         <v>104</v>
       </c>
       <c r="P51" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.2</v>
       </c>
       <c r="Q51" s="5"/>
@@ -6576,7 +6715,7 @@
         <v>86.666666666666671</v>
       </c>
       <c r="T51" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>86.666666666666671</v>
       </c>
       <c r="U51" s="1">
@@ -6616,7 +6755,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG51" s="1"/>
+      <c r="AG51" s="1">
+        <f t="shared" si="8"/>
+        <v>0.39600000000000002</v>
+      </c>
       <c r="AH51" s="1"/>
       <c r="AI51" s="1"/>
       <c r="AJ51" s="1"/>
@@ -6667,7 +6809,7 @@
         <v>53</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-13</v>
       </c>
       <c r="M52" s="1"/>
@@ -6676,7 +6818,7 @@
         <v>232</v>
       </c>
       <c r="P52" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8</v>
       </c>
       <c r="Q52" s="5"/>
@@ -6689,7 +6831,7 @@
         <v>29.375</v>
       </c>
       <c r="T52" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>29.375</v>
       </c>
       <c r="U52" s="1">
@@ -6727,7 +6869,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG52" s="1"/>
+      <c r="AG52" s="1">
+        <f t="shared" si="8"/>
+        <v>3.2</v>
+      </c>
       <c r="AH52" s="1"/>
       <c r="AI52" s="1"/>
       <c r="AJ52" s="1"/>
@@ -6778,7 +6923,7 @@
         <v>61</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-13</v>
       </c>
       <c r="M53" s="1"/>
@@ -6787,11 +6932,11 @@
         <v>0</v>
       </c>
       <c r="P53" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.6</v>
       </c>
       <c r="Q53" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>65</v>
       </c>
       <c r="R53" s="5">
@@ -6803,7 +6948,7 @@
         <v>15</v>
       </c>
       <c r="T53" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.2291666666666679</v>
       </c>
       <c r="U53" s="1">
@@ -6841,7 +6986,10 @@
         <f t="shared" si="7"/>
         <v>21.45</v>
       </c>
-      <c r="AG53" s="1"/>
+      <c r="AG53" s="1">
+        <f t="shared" si="8"/>
+        <v>3.1680000000000001</v>
+      </c>
       <c r="AH53" s="1"/>
       <c r="AI53" s="1"/>
       <c r="AJ53" s="1"/>
@@ -6892,7 +7040,7 @@
         <v>413</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>39.802000000000021</v>
       </c>
       <c r="M54" s="1"/>
@@ -6901,7 +7049,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>90.560400000000001</v>
       </c>
       <c r="Q54" s="5">
@@ -6917,7 +7065,7 @@
         <v>13.998237640293111</v>
       </c>
       <c r="T54" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.0146156598248242</v>
       </c>
       <c r="U54" s="1">
@@ -6955,7 +7103,10 @@
         <f t="shared" si="7"/>
         <v>723</v>
       </c>
-      <c r="AG54" s="1"/>
+      <c r="AG54" s="1">
+        <f t="shared" si="8"/>
+        <v>90.560400000000001</v>
+      </c>
       <c r="AH54" s="1"/>
       <c r="AI54" s="1"/>
       <c r="AJ54" s="1"/>
@@ -7002,7 +7153,7 @@
         <v>13</v>
       </c>
       <c r="L55" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-13</v>
       </c>
       <c r="M55" s="9"/>
@@ -7011,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="P55" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q55" s="11"/>
@@ -7024,7 +7175,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T55" s="9" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U55" s="9">
@@ -7064,7 +7215,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG55" s="1"/>
+      <c r="AG55" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH55" s="1"/>
       <c r="AI55" s="1"/>
       <c r="AJ55" s="1"/>
@@ -7115,7 +7269,7 @@
         <v>91</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-69</v>
       </c>
       <c r="M56" s="1"/>
@@ -7124,7 +7278,7 @@
         <v>0</v>
       </c>
       <c r="P56" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="Q56" s="5">
@@ -7140,7 +7294,7 @@
         <v>12.954545454545453</v>
       </c>
       <c r="T56" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.4545454545454541</v>
       </c>
       <c r="U56" s="1">
@@ -7178,7 +7332,10 @@
         <f t="shared" si="7"/>
         <v>13.200000000000001</v>
       </c>
-      <c r="AG56" s="1"/>
+      <c r="AG56" s="1">
+        <f t="shared" si="8"/>
+        <v>1.7600000000000002</v>
+      </c>
       <c r="AH56" s="1"/>
       <c r="AI56" s="1"/>
       <c r="AJ56" s="1"/>
@@ -7227,7 +7384,7 @@
         <v>0.5</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.5</v>
       </c>
       <c r="M57" s="1"/>
@@ -7236,7 +7393,7 @@
         <v>6</v>
       </c>
       <c r="P57" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q57" s="5"/>
@@ -7249,7 +7406,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T57" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U57" s="1">
@@ -7287,7 +7444,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG57" s="1"/>
+      <c r="AG57" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH57" s="1"/>
       <c r="AI57" s="1"/>
       <c r="AJ57" s="1"/>
@@ -7334,7 +7494,7 @@
         <v>0.5</v>
       </c>
       <c r="L58" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.5</v>
       </c>
       <c r="M58" s="9"/>
@@ -7343,7 +7503,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q58" s="11"/>
@@ -7356,7 +7516,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T58" s="9" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U58" s="9">
@@ -7396,7 +7556,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG58" s="1"/>
+      <c r="AG58" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH58" s="1"/>
       <c r="AI58" s="1"/>
       <c r="AJ58" s="1"/>
@@ -7445,7 +7608,7 @@
         <v>33</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-8.9920000000000009</v>
       </c>
       <c r="M59" s="1"/>
@@ -7454,7 +7617,7 @@
         <v>88</v>
       </c>
       <c r="P59" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.8015999999999996</v>
       </c>
       <c r="Q59" s="5"/>
@@ -7467,7 +7630,7 @@
         <v>18.334513495501501</v>
       </c>
       <c r="T59" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>18.334513495501501</v>
       </c>
       <c r="U59" s="1">
@@ -7505,7 +7668,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG59" s="1"/>
+      <c r="AG59" s="1">
+        <f t="shared" si="8"/>
+        <v>4.8015999999999996</v>
+      </c>
       <c r="AH59" s="1"/>
       <c r="AI59" s="1"/>
       <c r="AJ59" s="1"/>
@@ -7544,7 +7710,7 @@
       <c r="J60" s="9"/>
       <c r="K60" s="9"/>
       <c r="L60" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M60" s="9"/>
@@ -7553,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="P60" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q60" s="11"/>
@@ -7566,7 +7732,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T60" s="9" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U60" s="9">
@@ -7606,7 +7772,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG60" s="1"/>
+      <c r="AG60" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AH60" s="1"/>
       <c r="AI60" s="1"/>
       <c r="AJ60" s="1"/>
@@ -7657,7 +7826,7 @@
         <v>17</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M61" s="1"/>
@@ -7666,7 +7835,7 @@
         <v>65</v>
       </c>
       <c r="P61" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.4</v>
       </c>
       <c r="Q61" s="5"/>
@@ -7679,7 +7848,7 @@
         <v>18.529411764705884</v>
       </c>
       <c r="T61" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>18.529411764705884</v>
       </c>
       <c r="U61" s="1">
@@ -7719,7 +7888,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG61" s="1"/>
+      <c r="AG61" s="1">
+        <f t="shared" si="8"/>
+        <v>0.85</v>
+      </c>
       <c r="AH61" s="1"/>
       <c r="AI61" s="1"/>
       <c r="AJ61" s="1"/>
@@ -7770,7 +7942,7 @@
         <v>56</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.71399999999999864</v>
       </c>
       <c r="M62" s="1"/>
@@ -7779,11 +7951,11 @@
         <v>0</v>
       </c>
       <c r="P62" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>11.0572</v>
       </c>
       <c r="Q62" s="5">
-        <f t="shared" ref="Q62:Q71" si="17">15*P62-O62-F62</f>
+        <f t="shared" ref="Q62:Q71" si="18">15*P62-O62-F62</f>
         <v>50.649000000000001</v>
       </c>
       <c r="R62" s="5">
@@ -7795,7 +7967,7 @@
         <v>15.031744021994719</v>
       </c>
       <c r="T62" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.419364757804869</v>
       </c>
       <c r="U62" s="1">
@@ -7833,7 +8005,10 @@
         <f t="shared" si="7"/>
         <v>51</v>
       </c>
-      <c r="AG62" s="1"/>
+      <c r="AG62" s="1">
+        <f t="shared" si="8"/>
+        <v>11.0572</v>
+      </c>
       <c r="AH62" s="1"/>
       <c r="AI62" s="1"/>
       <c r="AJ62" s="1"/>
@@ -7882,7 +8057,7 @@
         <v>98</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-30</v>
       </c>
       <c r="M63" s="1"/>
@@ -7891,11 +8066,11 @@
         <v>0</v>
       </c>
       <c r="P63" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.6</v>
       </c>
       <c r="Q63" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>107</v>
       </c>
       <c r="R63" s="5">
@@ -7907,7 +8082,7 @@
         <v>15</v>
       </c>
       <c r="T63" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.132352941176471</v>
       </c>
       <c r="U63" s="1">
@@ -7947,7 +8122,10 @@
         <f t="shared" si="7"/>
         <v>28.89</v>
       </c>
-      <c r="AG63" s="1"/>
+      <c r="AG63" s="1">
+        <f t="shared" si="8"/>
+        <v>3.6720000000000002</v>
+      </c>
       <c r="AH63" s="1"/>
       <c r="AI63" s="1"/>
       <c r="AJ63" s="1"/>
@@ -7998,7 +8176,7 @@
         <v>30</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-12</v>
       </c>
       <c r="M64" s="1"/>
@@ -8007,7 +8185,7 @@
         <v>174</v>
       </c>
       <c r="P64" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.6</v>
       </c>
       <c r="Q64" s="5"/>
@@ -8020,7 +8198,7 @@
         <v>77.222222222222214</v>
       </c>
       <c r="T64" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>77.222222222222214</v>
       </c>
       <c r="U64" s="1">
@@ -8060,7 +8238,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG64" s="1"/>
+      <c r="AG64" s="1">
+        <f t="shared" si="8"/>
+        <v>1.08</v>
+      </c>
       <c r="AH64" s="1"/>
       <c r="AI64" s="1"/>
       <c r="AJ64" s="1"/>
@@ -8112,7 +8293,7 @@
         <v>416</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-3</v>
       </c>
       <c r="M65" s="1"/>
@@ -8121,7 +8302,7 @@
         <v>300</v>
       </c>
       <c r="P65" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>82.6</v>
       </c>
       <c r="Q65" s="5">
@@ -8137,7 +8318,7 @@
         <v>13.002421307506054</v>
       </c>
       <c r="T65" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.3874092009685235</v>
       </c>
       <c r="U65" s="1">
@@ -8175,7 +8356,10 @@
         <f t="shared" si="7"/>
         <v>257.89</v>
       </c>
-      <c r="AG65" s="1"/>
+      <c r="AG65" s="1">
+        <f t="shared" si="8"/>
+        <v>33.865999999999993</v>
+      </c>
       <c r="AH65" s="1"/>
       <c r="AI65" s="1"/>
       <c r="AJ65" s="1"/>
@@ -8226,7 +8410,7 @@
         <v>137.5</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.6040000000000134</v>
       </c>
       <c r="M66" s="1"/>
@@ -8235,7 +8419,7 @@
         <v>0</v>
       </c>
       <c r="P66" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>28.420800000000003</v>
       </c>
       <c r="Q66" s="5"/>
@@ -8248,7 +8432,7 @@
         <v>15.026740978438324</v>
       </c>
       <c r="T66" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.026740978438324</v>
       </c>
       <c r="U66" s="1">
@@ -8288,7 +8472,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG66" s="1"/>
+      <c r="AG66" s="1">
+        <f t="shared" si="8"/>
+        <v>28.420800000000003</v>
+      </c>
       <c r="AH66" s="1"/>
       <c r="AI66" s="1"/>
       <c r="AJ66" s="1"/>
@@ -8339,7 +8526,7 @@
         <v>52</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-10</v>
       </c>
       <c r="M67" s="1"/>
@@ -8348,7 +8535,7 @@
         <v>189</v>
       </c>
       <c r="P67" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.4</v>
       </c>
       <c r="Q67" s="5"/>
@@ -8361,7 +8548,7 @@
         <v>25.714285714285712</v>
       </c>
       <c r="T67" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>25.714285714285712</v>
       </c>
       <c r="U67" s="1">
@@ -8399,7 +8586,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG67" s="1"/>
+      <c r="AG67" s="1">
+        <f t="shared" si="8"/>
+        <v>2.94</v>
+      </c>
       <c r="AH67" s="1"/>
       <c r="AI67" s="1"/>
       <c r="AJ67" s="1"/>
@@ -8448,7 +8638,7 @@
         <v>20</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.4869999999999983</v>
       </c>
       <c r="M68" s="1"/>
@@ -8457,7 +8647,7 @@
         <v>68</v>
       </c>
       <c r="P68" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.2973999999999997</v>
       </c>
       <c r="Q68" s="5"/>
@@ -8470,7 +8660,7 @@
         <v>16.146600218975347</v>
       </c>
       <c r="T68" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>16.146600218975347</v>
       </c>
       <c r="U68" s="1">
@@ -8508,7 +8698,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG68" s="1"/>
+      <c r="AG68" s="1">
+        <f t="shared" si="8"/>
+        <v>5.2973999999999997</v>
+      </c>
       <c r="AH68" s="1"/>
       <c r="AI68" s="1"/>
       <c r="AJ68" s="1"/>
@@ -8559,7 +8752,7 @@
         <v>219</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-183</v>
       </c>
       <c r="M69" s="1"/>
@@ -8568,7 +8761,7 @@
         <v>307</v>
       </c>
       <c r="P69" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.2</v>
       </c>
       <c r="Q69" s="5"/>
@@ -8581,7 +8774,7 @@
         <v>42.777777777777779</v>
       </c>
       <c r="T69" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>42.777777777777779</v>
       </c>
       <c r="U69" s="1">
@@ -8619,7 +8812,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG69" s="1"/>
+      <c r="AG69" s="1">
+        <f t="shared" si="8"/>
+        <v>2.952</v>
+      </c>
       <c r="AH69" s="1"/>
       <c r="AI69" s="1"/>
       <c r="AJ69" s="1"/>
@@ -8670,7 +8866,7 @@
         <v>167.5</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="18">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="19">E70-K70</f>
         <v>14.308999999999997</v>
       </c>
       <c r="M70" s="1"/>
@@ -8679,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="1">
-        <f t="shared" ref="P70:P101" si="19">E70/5</f>
+        <f t="shared" ref="P70:P101" si="20">E70/5</f>
         <v>36.361800000000002</v>
       </c>
       <c r="Q70" s="5">
@@ -8695,7 +8891,7 @@
         <v>13.013657189688079</v>
       </c>
       <c r="T70" s="1">
-        <f t="shared" ref="T70:T101" si="20">(F70+O70)/P70</f>
+        <f t="shared" ref="T70:T101" si="21">(F70+O70)/P70</f>
         <v>5.4782766529709743</v>
       </c>
       <c r="U70" s="1">
@@ -8733,7 +8929,10 @@
         <f t="shared" si="7"/>
         <v>274</v>
       </c>
-      <c r="AG70" s="1"/>
+      <c r="AG70" s="1">
+        <f t="shared" si="8"/>
+        <v>36.361800000000002</v>
+      </c>
       <c r="AH70" s="1"/>
       <c r="AI70" s="1"/>
       <c r="AJ70" s="1"/>
@@ -8784,7 +8983,7 @@
         <v>80</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M71" s="1"/>
@@ -8793,23 +8992,23 @@
         <v>161</v>
       </c>
       <c r="P71" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16.2</v>
       </c>
       <c r="Q71" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>18</v>
       </c>
       <c r="R71" s="5">
-        <f t="shared" ref="R71:R112" si="21">ROUND(Q71,0)</f>
+        <f t="shared" ref="R71:R112" si="22">ROUND(Q71,0)</f>
         <v>18</v>
       </c>
       <c r="S71" s="1">
-        <f t="shared" ref="S71:S112" si="22">(F71+O71+R71)/P71</f>
+        <f t="shared" ref="S71:S112" si="23">(F71+O71+R71)/P71</f>
         <v>15</v>
       </c>
       <c r="T71" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.888888888888889</v>
       </c>
       <c r="U71" s="1">
@@ -8844,10 +9043,13 @@
       </c>
       <c r="AE71" s="1"/>
       <c r="AF71" s="1">
-        <f t="shared" ref="AF71:AF112" si="23">G71*R71</f>
+        <f t="shared" ref="AF71:AF112" si="24">G71*R71</f>
         <v>5.3999999999999995</v>
       </c>
-      <c r="AG71" s="1"/>
+      <c r="AG71" s="1">
+        <f t="shared" ref="AG71:AG112" si="25">P71*G71</f>
+        <v>4.8599999999999994</v>
+      </c>
       <c r="AH71" s="1"/>
       <c r="AI71" s="1"/>
       <c r="AJ71" s="1"/>
@@ -8892,7 +9094,7 @@
       <c r="J72" s="9"/>
       <c r="K72" s="9"/>
       <c r="L72" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M72" s="9"/>
@@ -8901,20 +9103,20 @@
         <v>0</v>
       </c>
       <c r="P72" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q72" s="11"/>
       <c r="R72" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S72" s="1" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T72" s="9" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S72" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T72" s="9" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U72" s="9">
@@ -8949,10 +9151,13 @@
       </c>
       <c r="AE72" s="9"/>
       <c r="AF72" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG72" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG72" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH72" s="1"/>
       <c r="AI72" s="1"/>
       <c r="AJ72" s="1"/>
@@ -9003,7 +9208,7 @@
         <v>202</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-18</v>
       </c>
       <c r="M73" s="1"/>
@@ -9012,7 +9217,7 @@
         <v>0</v>
       </c>
       <c r="P73" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>36.799999999999997</v>
       </c>
       <c r="Q73" s="5">
@@ -9020,15 +9225,15 @@
         <v>281.39999999999998</v>
       </c>
       <c r="R73" s="5">
+        <f t="shared" si="22"/>
+        <v>281</v>
+      </c>
+      <c r="S73" s="1">
+        <f t="shared" si="23"/>
+        <v>12.989130434782609</v>
+      </c>
+      <c r="T73" s="1">
         <f t="shared" si="21"/>
-        <v>281</v>
-      </c>
-      <c r="S73" s="1">
-        <f t="shared" si="22"/>
-        <v>12.989130434782609</v>
-      </c>
-      <c r="T73" s="1">
-        <f t="shared" si="20"/>
         <v>5.3532608695652177</v>
       </c>
       <c r="U73" s="1">
@@ -9063,10 +9268,13 @@
       </c>
       <c r="AE73" s="1"/>
       <c r="AF73" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>50.58</v>
       </c>
-      <c r="AG73" s="1"/>
+      <c r="AG73" s="1">
+        <f t="shared" si="25"/>
+        <v>6.6239999999999997</v>
+      </c>
       <c r="AH73" s="1"/>
       <c r="AI73" s="1"/>
       <c r="AJ73" s="1"/>
@@ -9117,7 +9325,7 @@
         <v>15</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="M74" s="1"/>
@@ -9126,20 +9334,20 @@
         <v>0</v>
       </c>
       <c r="P74" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
       <c r="Q74" s="5"/>
       <c r="R74" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S74" s="1">
+        <f t="shared" si="23"/>
+        <v>17.75</v>
+      </c>
+      <c r="T74" s="1">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S74" s="1">
-        <f t="shared" si="22"/>
-        <v>17.75</v>
-      </c>
-      <c r="T74" s="1">
-        <f t="shared" si="20"/>
         <v>17.75</v>
       </c>
       <c r="U74" s="1">
@@ -9176,10 +9384,13 @@
         <v>56</v>
       </c>
       <c r="AF74" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG74" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG74" s="1">
+        <f t="shared" si="25"/>
+        <v>3.36</v>
+      </c>
       <c r="AH74" s="1"/>
       <c r="AI74" s="1"/>
       <c r="AJ74" s="1"/>
@@ -9230,7 +9441,7 @@
         <v>374</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-4</v>
       </c>
       <c r="M75" s="1"/>
@@ -9239,23 +9450,23 @@
         <v>383</v>
       </c>
       <c r="P75" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>74</v>
       </c>
       <c r="Q75" s="5">
-        <f t="shared" ref="Q75" si="24">15*P75-O75-F75</f>
+        <f t="shared" ref="Q75" si="26">15*P75-O75-F75</f>
         <v>411</v>
       </c>
       <c r="R75" s="5">
+        <f t="shared" si="22"/>
+        <v>411</v>
+      </c>
+      <c r="S75" s="1">
+        <f t="shared" si="23"/>
+        <v>15</v>
+      </c>
+      <c r="T75" s="1">
         <f t="shared" si="21"/>
-        <v>411</v>
-      </c>
-      <c r="S75" s="1">
-        <f t="shared" si="22"/>
-        <v>15</v>
-      </c>
-      <c r="T75" s="1">
-        <f t="shared" si="20"/>
         <v>9.4459459459459456</v>
       </c>
       <c r="U75" s="1">
@@ -9290,10 +9501,13 @@
       </c>
       <c r="AE75" s="1"/>
       <c r="AF75" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>143.85</v>
       </c>
-      <c r="AG75" s="1"/>
+      <c r="AG75" s="1">
+        <f t="shared" si="25"/>
+        <v>25.9</v>
+      </c>
       <c r="AH75" s="1"/>
       <c r="AI75" s="1"/>
       <c r="AJ75" s="1"/>
@@ -9332,7 +9546,7 @@
       <c r="J76" s="9"/>
       <c r="K76" s="9"/>
       <c r="L76" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M76" s="9"/>
@@ -9341,20 +9555,20 @@
         <v>0</v>
       </c>
       <c r="P76" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q76" s="11"/>
       <c r="R76" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S76" s="1" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T76" s="9" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S76" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T76" s="9" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U76" s="9">
@@ -9391,10 +9605,13 @@
         <v>88</v>
       </c>
       <c r="AF76" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG76" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG76" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH76" s="1"/>
       <c r="AI76" s="1"/>
       <c r="AJ76" s="1"/>
@@ -9445,7 +9662,7 @@
         <v>109.7</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10.158999999999992</v>
       </c>
       <c r="M77" s="1"/>
@@ -9454,23 +9671,23 @@
         <v>0</v>
       </c>
       <c r="P77" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>23.971799999999998</v>
       </c>
       <c r="Q77" s="5">
-        <f t="shared" ref="Q77:Q84" si="25">15*P77-O77-F77</f>
+        <f t="shared" ref="Q77:Q84" si="27">15*P77-O77-F77</f>
         <v>102.815</v>
       </c>
       <c r="R77" s="5">
+        <f t="shared" si="22"/>
+        <v>103</v>
+      </c>
+      <c r="S77" s="1">
+        <f t="shared" si="23"/>
+        <v>15.007717401279839</v>
+      </c>
+      <c r="T77" s="1">
         <f t="shared" si="21"/>
-        <v>103</v>
-      </c>
-      <c r="S77" s="1">
-        <f t="shared" si="22"/>
-        <v>15.007717401279839</v>
-      </c>
-      <c r="T77" s="1">
-        <f t="shared" si="20"/>
         <v>10.711002094127267</v>
       </c>
       <c r="U77" s="1">
@@ -9505,10 +9722,13 @@
       </c>
       <c r="AE77" s="1"/>
       <c r="AF77" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>103</v>
       </c>
-      <c r="AG77" s="1"/>
+      <c r="AG77" s="1">
+        <f t="shared" si="25"/>
+        <v>23.971799999999998</v>
+      </c>
       <c r="AH77" s="1"/>
       <c r="AI77" s="1"/>
       <c r="AJ77" s="1"/>
@@ -9559,7 +9779,7 @@
         <v>170.8</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>26.072000000000003</v>
       </c>
       <c r="M78" s="1"/>
@@ -9568,23 +9788,23 @@
         <v>0</v>
       </c>
       <c r="P78" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>39.374400000000001</v>
       </c>
       <c r="Q78" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>284.69299999999998</v>
       </c>
       <c r="R78" s="5">
+        <f t="shared" si="22"/>
+        <v>285</v>
+      </c>
+      <c r="S78" s="1">
+        <f t="shared" si="23"/>
+        <v>15.007796944207403</v>
+      </c>
+      <c r="T78" s="1">
         <f t="shared" si="21"/>
-        <v>285</v>
-      </c>
-      <c r="S78" s="1">
-        <f t="shared" si="22"/>
-        <v>15.007796944207403</v>
-      </c>
-      <c r="T78" s="1">
-        <f t="shared" si="20"/>
         <v>7.7695914096468766</v>
       </c>
       <c r="U78" s="1">
@@ -9619,10 +9839,13 @@
       </c>
       <c r="AE78" s="1"/>
       <c r="AF78" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>285</v>
       </c>
-      <c r="AG78" s="1"/>
+      <c r="AG78" s="1">
+        <f t="shared" si="25"/>
+        <v>39.374400000000001</v>
+      </c>
       <c r="AH78" s="1"/>
       <c r="AI78" s="1"/>
       <c r="AJ78" s="1"/>
@@ -9673,7 +9896,7 @@
         <v>398</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-6</v>
       </c>
       <c r="M79" s="1"/>
@@ -9682,7 +9905,7 @@
         <v>37</v>
       </c>
       <c r="P79" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>78.400000000000006</v>
       </c>
       <c r="Q79" s="5">
@@ -9690,15 +9913,15 @@
         <v>597.20000000000005</v>
       </c>
       <c r="R79" s="5">
+        <f t="shared" si="22"/>
+        <v>597</v>
+      </c>
+      <c r="S79" s="1">
+        <f t="shared" si="23"/>
+        <v>12.997448979591836</v>
+      </c>
+      <c r="T79" s="1">
         <f t="shared" si="21"/>
-        <v>597</v>
-      </c>
-      <c r="S79" s="1">
-        <f t="shared" si="22"/>
-        <v>12.997448979591836</v>
-      </c>
-      <c r="T79" s="1">
-        <f t="shared" si="20"/>
         <v>5.3826530612244898</v>
       </c>
       <c r="U79" s="1">
@@ -9733,10 +9956,13 @@
       </c>
       <c r="AE79" s="1"/>
       <c r="AF79" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>208.95</v>
       </c>
-      <c r="AG79" s="1"/>
+      <c r="AG79" s="1">
+        <f t="shared" si="25"/>
+        <v>27.44</v>
+      </c>
       <c r="AH79" s="1"/>
       <c r="AI79" s="1"/>
       <c r="AJ79" s="1"/>
@@ -9787,7 +10013,7 @@
         <v>89</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="M80" s="1"/>
@@ -9796,23 +10022,23 @@
         <v>121</v>
       </c>
       <c r="P80" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>18.2</v>
       </c>
       <c r="Q80" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>107</v>
       </c>
       <c r="R80" s="5">
+        <f t="shared" si="22"/>
+        <v>107</v>
+      </c>
+      <c r="S80" s="1">
+        <f t="shared" si="23"/>
+        <v>15</v>
+      </c>
+      <c r="T80" s="1">
         <f t="shared" si="21"/>
-        <v>107</v>
-      </c>
-      <c r="S80" s="1">
-        <f t="shared" si="22"/>
-        <v>15</v>
-      </c>
-      <c r="T80" s="1">
-        <f t="shared" si="20"/>
         <v>9.1208791208791204</v>
       </c>
       <c r="U80" s="1">
@@ -9847,10 +10073,13 @@
       </c>
       <c r="AE80" s="1"/>
       <c r="AF80" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>32.1</v>
       </c>
-      <c r="AG80" s="1"/>
+      <c r="AG80" s="1">
+        <f t="shared" si="25"/>
+        <v>5.46</v>
+      </c>
       <c r="AH80" s="1"/>
       <c r="AI80" s="1"/>
       <c r="AJ80" s="1"/>
@@ -9897,7 +10126,7 @@
         <v>48</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-47</v>
       </c>
       <c r="M81" s="1"/>
@@ -9906,20 +10135,20 @@
         <v>188</v>
       </c>
       <c r="P81" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.2</v>
       </c>
       <c r="Q81" s="5"/>
       <c r="R81" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S81" s="1">
+        <f t="shared" si="23"/>
+        <v>940</v>
+      </c>
+      <c r="T81" s="1">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S81" s="1">
-        <f t="shared" si="22"/>
-        <v>940</v>
-      </c>
-      <c r="T81" s="1">
-        <f t="shared" si="20"/>
         <v>940</v>
       </c>
       <c r="U81" s="1">
@@ -9954,10 +10183,13 @@
       </c>
       <c r="AE81" s="1"/>
       <c r="AF81" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG81" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG81" s="1">
+        <f t="shared" si="25"/>
+        <v>0.06</v>
+      </c>
       <c r="AH81" s="1"/>
       <c r="AI81" s="1"/>
       <c r="AJ81" s="1"/>
@@ -10008,7 +10240,7 @@
         <v>327</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="M82" s="1"/>
@@ -10017,23 +10249,23 @@
         <v>467</v>
       </c>
       <c r="P82" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>66</v>
       </c>
       <c r="Q82" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>375</v>
       </c>
       <c r="R82" s="5">
+        <f t="shared" si="22"/>
+        <v>375</v>
+      </c>
+      <c r="S82" s="1">
+        <f t="shared" si="23"/>
+        <v>15</v>
+      </c>
+      <c r="T82" s="1">
         <f t="shared" si="21"/>
-        <v>375</v>
-      </c>
-      <c r="S82" s="1">
-        <f t="shared" si="22"/>
-        <v>15</v>
-      </c>
-      <c r="T82" s="1">
-        <f t="shared" si="20"/>
         <v>9.3181818181818183</v>
       </c>
       <c r="U82" s="1">
@@ -10068,10 +10300,13 @@
       </c>
       <c r="AE82" s="1"/>
       <c r="AF82" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>105.00000000000001</v>
       </c>
-      <c r="AG82" s="1"/>
+      <c r="AG82" s="1">
+        <f t="shared" si="25"/>
+        <v>18.48</v>
+      </c>
       <c r="AH82" s="1"/>
       <c r="AI82" s="1"/>
       <c r="AJ82" s="1"/>
@@ -10122,7 +10357,7 @@
         <v>279</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-22</v>
       </c>
       <c r="M83" s="1"/>
@@ -10131,23 +10366,23 @@
         <v>332</v>
       </c>
       <c r="P83" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>51.4</v>
       </c>
       <c r="Q83" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>206</v>
       </c>
       <c r="R83" s="5">
+        <f t="shared" si="22"/>
+        <v>206</v>
+      </c>
+      <c r="S83" s="1">
+        <f t="shared" si="23"/>
+        <v>15</v>
+      </c>
+      <c r="T83" s="1">
         <f t="shared" si="21"/>
-        <v>206</v>
-      </c>
-      <c r="S83" s="1">
-        <f t="shared" si="22"/>
-        <v>15</v>
-      </c>
-      <c r="T83" s="1">
-        <f t="shared" si="20"/>
         <v>10.992217898832685</v>
       </c>
       <c r="U83" s="1">
@@ -10182,10 +10417,13 @@
       </c>
       <c r="AE83" s="1"/>
       <c r="AF83" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>57.680000000000007</v>
       </c>
-      <c r="AG83" s="1"/>
+      <c r="AG83" s="1">
+        <f t="shared" si="25"/>
+        <v>14.392000000000001</v>
+      </c>
       <c r="AH83" s="1"/>
       <c r="AI83" s="1"/>
       <c r="AJ83" s="1"/>
@@ -10236,7 +10474,7 @@
         <v>255</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-5</v>
       </c>
       <c r="M84" s="1"/>
@@ -10245,23 +10483,23 @@
         <v>289</v>
       </c>
       <c r="P84" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>50</v>
       </c>
       <c r="Q84" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>321</v>
       </c>
       <c r="R84" s="5">
+        <f t="shared" si="22"/>
+        <v>321</v>
+      </c>
+      <c r="S84" s="1">
+        <f t="shared" si="23"/>
+        <v>15</v>
+      </c>
+      <c r="T84" s="1">
         <f t="shared" si="21"/>
-        <v>321</v>
-      </c>
-      <c r="S84" s="1">
-        <f t="shared" si="22"/>
-        <v>15</v>
-      </c>
-      <c r="T84" s="1">
-        <f t="shared" si="20"/>
         <v>8.58</v>
       </c>
       <c r="U84" s="1">
@@ -10296,10 +10534,13 @@
       </c>
       <c r="AE84" s="1"/>
       <c r="AF84" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>89.88000000000001</v>
       </c>
-      <c r="AG84" s="1"/>
+      <c r="AG84" s="1">
+        <f t="shared" si="25"/>
+        <v>14.000000000000002</v>
+      </c>
       <c r="AH84" s="1"/>
       <c r="AI84" s="1"/>
       <c r="AJ84" s="1"/>
@@ -10350,7 +10591,7 @@
         <v>341</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>28</v>
       </c>
       <c r="M85" s="1"/>
@@ -10359,7 +10600,7 @@
         <v>109</v>
       </c>
       <c r="P85" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>73.8</v>
       </c>
       <c r="Q85" s="5">
@@ -10367,15 +10608,15 @@
         <v>615.79999999999995</v>
       </c>
       <c r="R85" s="5">
+        <f t="shared" si="22"/>
+        <v>616</v>
+      </c>
+      <c r="S85" s="1">
+        <f t="shared" si="23"/>
+        <v>11.002710027100271</v>
+      </c>
+      <c r="T85" s="1">
         <f t="shared" si="21"/>
-        <v>616</v>
-      </c>
-      <c r="S85" s="1">
-        <f t="shared" si="22"/>
-        <v>11.002710027100271</v>
-      </c>
-      <c r="T85" s="1">
-        <f t="shared" si="20"/>
         <v>2.6558265582655829</v>
       </c>
       <c r="U85" s="1">
@@ -10410,10 +10651,13 @@
       </c>
       <c r="AE85" s="1"/>
       <c r="AF85" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>246.4</v>
       </c>
-      <c r="AG85" s="1"/>
+      <c r="AG85" s="1">
+        <f t="shared" si="25"/>
+        <v>29.52</v>
+      </c>
       <c r="AH85" s="1"/>
       <c r="AI85" s="1"/>
       <c r="AJ85" s="1"/>
@@ -10460,7 +10704,7 @@
         <v>9</v>
       </c>
       <c r="L86" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-9</v>
       </c>
       <c r="M86" s="9"/>
@@ -10469,20 +10713,20 @@
         <v>0</v>
       </c>
       <c r="P86" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q86" s="11"/>
       <c r="R86" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S86" s="1" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T86" s="9" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S86" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T86" s="9" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U86" s="9">
@@ -10517,10 +10761,13 @@
       </c>
       <c r="AE86" s="9"/>
       <c r="AF86" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG86" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG86" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH86" s="1"/>
       <c r="AI86" s="1"/>
       <c r="AJ86" s="1"/>
@@ -10569,7 +10816,7 @@
         <v>14</v>
       </c>
       <c r="L87" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-16</v>
       </c>
       <c r="M87" s="9"/>
@@ -10578,20 +10825,20 @@
         <v>0</v>
       </c>
       <c r="P87" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-0.4</v>
       </c>
       <c r="Q87" s="11"/>
       <c r="R87" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S87" s="1">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="T87" s="9">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S87" s="1">
-        <f t="shared" si="22"/>
-        <v>5</v>
-      </c>
-      <c r="T87" s="9">
-        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="U87" s="9">
@@ -10626,10 +10873,13 @@
       </c>
       <c r="AE87" s="9"/>
       <c r="AF87" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG87" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG87" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH87" s="1"/>
       <c r="AI87" s="1"/>
       <c r="AJ87" s="1"/>
@@ -10678,7 +10928,7 @@
         <v>4</v>
       </c>
       <c r="L88" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-4</v>
       </c>
       <c r="M88" s="9"/>
@@ -10687,20 +10937,20 @@
         <v>0</v>
       </c>
       <c r="P88" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q88" s="11"/>
       <c r="R88" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S88" s="1" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T88" s="9" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S88" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T88" s="9" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U88" s="9">
@@ -10737,10 +10987,13 @@
         <v>136</v>
       </c>
       <c r="AF88" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG88" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG88" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH88" s="1"/>
       <c r="AI88" s="1"/>
       <c r="AJ88" s="1"/>
@@ -10787,7 +11040,7 @@
         <v>5</v>
       </c>
       <c r="L89" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-5.8029999999999999</v>
       </c>
       <c r="M89" s="9"/>
@@ -10796,20 +11049,20 @@
         <v>0</v>
       </c>
       <c r="P89" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-0.16060000000000002</v>
       </c>
       <c r="Q89" s="11"/>
       <c r="R89" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S89" s="1">
+        <f t="shared" si="23"/>
+        <v>-1.8742216687422164</v>
+      </c>
+      <c r="T89" s="9">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S89" s="1">
-        <f t="shared" si="22"/>
-        <v>-1.8742216687422164</v>
-      </c>
-      <c r="T89" s="9">
-        <f t="shared" si="20"/>
         <v>-1.8742216687422164</v>
       </c>
       <c r="U89" s="9">
@@ -10846,10 +11099,13 @@
         <v>138</v>
       </c>
       <c r="AF89" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG89" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG89" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH89" s="1"/>
       <c r="AI89" s="1"/>
       <c r="AJ89" s="1"/>
@@ -10900,7 +11156,7 @@
         <v>82</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-32</v>
       </c>
       <c r="M90" s="1"/>
@@ -10909,20 +11165,20 @@
         <v>279</v>
       </c>
       <c r="P90" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="Q90" s="5"/>
       <c r="R90" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S90" s="1">
+        <f t="shared" si="23"/>
+        <v>38.1</v>
+      </c>
+      <c r="T90" s="1">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S90" s="1">
-        <f t="shared" si="22"/>
-        <v>38.1</v>
-      </c>
-      <c r="T90" s="1">
-        <f t="shared" si="20"/>
         <v>38.1</v>
       </c>
       <c r="U90" s="1">
@@ -10957,10 +11213,13 @@
       </c>
       <c r="AE90" s="1"/>
       <c r="AF90" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG90" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG90" s="1">
+        <f t="shared" si="25"/>
+        <v>2.8000000000000003</v>
+      </c>
       <c r="AH90" s="1"/>
       <c r="AI90" s="1"/>
       <c r="AJ90" s="1"/>
@@ -11007,7 +11266,7 @@
         <v>5</v>
       </c>
       <c r="L91" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-5</v>
       </c>
       <c r="M91" s="9"/>
@@ -11016,20 +11275,20 @@
         <v>0</v>
       </c>
       <c r="P91" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q91" s="11"/>
       <c r="R91" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S91" s="1" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T91" s="9" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S91" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T91" s="9" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U91" s="9">
@@ -11064,10 +11323,13 @@
       </c>
       <c r="AE91" s="9"/>
       <c r="AF91" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG91" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG91" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH91" s="1"/>
       <c r="AI91" s="1"/>
       <c r="AJ91" s="1"/>
@@ -11118,7 +11380,7 @@
         <v>15</v>
       </c>
       <c r="L92" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-6</v>
       </c>
       <c r="M92" s="9"/>
@@ -11127,20 +11389,20 @@
         <v>0</v>
       </c>
       <c r="P92" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.8</v>
       </c>
       <c r="Q92" s="11"/>
       <c r="R92" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S92" s="1">
+        <f t="shared" si="23"/>
+        <v>3.8888888888888888</v>
+      </c>
+      <c r="T92" s="9">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S92" s="1">
-        <f t="shared" si="22"/>
-        <v>3.8888888888888888</v>
-      </c>
-      <c r="T92" s="9">
-        <f t="shared" si="20"/>
         <v>3.8888888888888888</v>
       </c>
       <c r="U92" s="9">
@@ -11175,10 +11437,13 @@
       </c>
       <c r="AE92" s="9"/>
       <c r="AF92" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG92" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG92" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH92" s="1"/>
       <c r="AI92" s="1"/>
       <c r="AJ92" s="1"/>
@@ -11229,7 +11494,7 @@
         <v>267</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-14</v>
       </c>
       <c r="M93" s="1"/>
@@ -11238,7 +11503,7 @@
         <v>0</v>
       </c>
       <c r="P93" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>50.6</v>
       </c>
       <c r="Q93" s="5">
@@ -11246,15 +11511,15 @@
         <v>253.39999999999998</v>
       </c>
       <c r="R93" s="5">
+        <f t="shared" si="22"/>
+        <v>253</v>
+      </c>
+      <c r="S93" s="1">
+        <f t="shared" si="23"/>
+        <v>13.992094861660078</v>
+      </c>
+      <c r="T93" s="1">
         <f t="shared" si="21"/>
-        <v>253</v>
-      </c>
-      <c r="S93" s="1">
-        <f t="shared" si="22"/>
-        <v>13.992094861660078</v>
-      </c>
-      <c r="T93" s="1">
-        <f t="shared" si="20"/>
         <v>8.9920948616600782</v>
       </c>
       <c r="U93" s="1">
@@ -11289,10 +11554,13 @@
       </c>
       <c r="AE93" s="1"/>
       <c r="AF93" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>30.36</v>
       </c>
-      <c r="AG93" s="1"/>
+      <c r="AG93" s="1">
+        <f t="shared" si="25"/>
+        <v>6.0720000000000001</v>
+      </c>
       <c r="AH93" s="1"/>
       <c r="AI93" s="1"/>
       <c r="AJ93" s="1"/>
@@ -11343,7 +11611,7 @@
         <v>65</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-11</v>
       </c>
       <c r="M94" s="1"/>
@@ -11352,7 +11620,7 @@
         <v>23</v>
       </c>
       <c r="P94" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.8</v>
       </c>
       <c r="Q94" s="5">
@@ -11360,15 +11628,15 @@
         <v>69.400000000000006</v>
       </c>
       <c r="R94" s="5">
+        <f t="shared" si="22"/>
+        <v>69</v>
+      </c>
+      <c r="S94" s="1">
+        <f t="shared" si="23"/>
+        <v>7.9629629629629628</v>
+      </c>
+      <c r="T94" s="1">
         <f t="shared" si="21"/>
-        <v>69</v>
-      </c>
-      <c r="S94" s="1">
-        <f t="shared" si="22"/>
-        <v>7.9629629629629628</v>
-      </c>
-      <c r="T94" s="1">
-        <f t="shared" si="20"/>
         <v>1.574074074074074</v>
       </c>
       <c r="U94" s="1">
@@ -11405,10 +11673,13 @@
         <v>170</v>
       </c>
       <c r="AF94" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>22.77</v>
       </c>
-      <c r="AG94" s="1"/>
+      <c r="AG94" s="1">
+        <f t="shared" si="25"/>
+        <v>3.5640000000000005</v>
+      </c>
       <c r="AH94" s="1"/>
       <c r="AI94" s="1"/>
       <c r="AJ94" s="1"/>
@@ -11449,7 +11720,7 @@
       <c r="J95" s="9"/>
       <c r="K95" s="9"/>
       <c r="L95" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M95" s="9"/>
@@ -11458,20 +11729,20 @@
         <v>0</v>
       </c>
       <c r="P95" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q95" s="11"/>
       <c r="R95" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S95" s="1" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T95" s="9" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S95" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T95" s="9" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U95" s="9">
@@ -11508,10 +11779,13 @@
         <v>88</v>
       </c>
       <c r="AF95" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG95" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG95" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH95" s="1"/>
       <c r="AI95" s="1"/>
       <c r="AJ95" s="1"/>
@@ -11560,7 +11834,7 @@
         <v>8</v>
       </c>
       <c r="L96" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-11</v>
       </c>
       <c r="M96" s="9"/>
@@ -11569,20 +11843,20 @@
         <v>0</v>
       </c>
       <c r="P96" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-0.6</v>
       </c>
       <c r="Q96" s="11"/>
       <c r="R96" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S96" s="1">
+        <f t="shared" si="23"/>
+        <v>11.666666666666668</v>
+      </c>
+      <c r="T96" s="9">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S96" s="1">
-        <f t="shared" si="22"/>
-        <v>11.666666666666668</v>
-      </c>
-      <c r="T96" s="9">
-        <f t="shared" si="20"/>
         <v>11.666666666666668</v>
       </c>
       <c r="U96" s="9">
@@ -11619,10 +11893,13 @@
         <v>146</v>
       </c>
       <c r="AF96" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG96" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG96" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH96" s="1"/>
       <c r="AI96" s="1"/>
       <c r="AJ96" s="1"/>
@@ -11663,7 +11940,7 @@
       <c r="J97" s="9"/>
       <c r="K97" s="9"/>
       <c r="L97" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M97" s="9"/>
@@ -11672,20 +11949,20 @@
         <v>0</v>
       </c>
       <c r="P97" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q97" s="11"/>
       <c r="R97" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S97" s="1" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T97" s="9" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S97" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T97" s="9" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U97" s="9">
@@ -11722,10 +11999,13 @@
         <v>88</v>
       </c>
       <c r="AF97" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG97" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG97" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH97" s="1"/>
       <c r="AI97" s="1"/>
       <c r="AJ97" s="1"/>
@@ -11766,7 +12046,7 @@
       <c r="J98" s="9"/>
       <c r="K98" s="9"/>
       <c r="L98" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M98" s="9"/>
@@ -11775,20 +12055,20 @@
         <v>0</v>
       </c>
       <c r="P98" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q98" s="11"/>
       <c r="R98" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S98" s="1" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T98" s="9" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S98" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T98" s="9" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U98" s="9">
@@ -11825,10 +12105,13 @@
         <v>88</v>
       </c>
       <c r="AF98" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG98" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG98" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH98" s="1"/>
       <c r="AI98" s="1"/>
       <c r="AJ98" s="1"/>
@@ -11879,7 +12162,7 @@
         <v>53</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-3</v>
       </c>
       <c r="M99" s="1"/>
@@ -11888,7 +12171,7 @@
         <v>0</v>
       </c>
       <c r="P99" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="Q99" s="5">
@@ -11896,15 +12179,15 @@
         <v>82</v>
       </c>
       <c r="R99" s="5">
+        <f t="shared" si="22"/>
+        <v>82</v>
+      </c>
+      <c r="S99" s="1">
+        <f t="shared" si="23"/>
+        <v>9</v>
+      </c>
+      <c r="T99" s="1">
         <f t="shared" si="21"/>
-        <v>82</v>
-      </c>
-      <c r="S99" s="1">
-        <f t="shared" si="22"/>
-        <v>9</v>
-      </c>
-      <c r="T99" s="1">
-        <f t="shared" si="20"/>
         <v>0.8</v>
       </c>
       <c r="U99" s="1">
@@ -11939,10 +12222,13 @@
       </c>
       <c r="AE99" s="1"/>
       <c r="AF99" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>32.800000000000004</v>
       </c>
-      <c r="AG99" s="1"/>
+      <c r="AG99" s="1">
+        <f t="shared" si="25"/>
+        <v>4</v>
+      </c>
       <c r="AH99" s="1"/>
       <c r="AI99" s="1"/>
       <c r="AJ99" s="1"/>
@@ -11989,7 +12275,7 @@
         <v>33</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-13</v>
       </c>
       <c r="M100" s="1"/>
@@ -11998,20 +12284,20 @@
         <v>183</v>
       </c>
       <c r="P100" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
       <c r="Q100" s="5"/>
       <c r="R100" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S100" s="1">
+        <f t="shared" si="23"/>
+        <v>45.75</v>
+      </c>
+      <c r="T100" s="1">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S100" s="1">
-        <f t="shared" si="22"/>
-        <v>45.75</v>
-      </c>
-      <c r="T100" s="1">
-        <f t="shared" si="20"/>
         <v>45.75</v>
       </c>
       <c r="U100" s="1">
@@ -12046,10 +12332,13 @@
       </c>
       <c r="AE100" s="1"/>
       <c r="AF100" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG100" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG100" s="1">
+        <f t="shared" si="25"/>
+        <v>1.4</v>
+      </c>
       <c r="AH100" s="1"/>
       <c r="AI100" s="1"/>
       <c r="AJ100" s="1"/>
@@ -12090,7 +12379,7 @@
       <c r="J101" s="9"/>
       <c r="K101" s="9"/>
       <c r="L101" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M101" s="9"/>
@@ -12099,20 +12388,20 @@
         <v>0</v>
       </c>
       <c r="P101" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q101" s="11"/>
       <c r="R101" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S101" s="1" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T101" s="9" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="S101" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T101" s="9" t="e">
-        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U101" s="9">
@@ -12149,10 +12438,13 @@
         <v>88</v>
       </c>
       <c r="AF101" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG101" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG101" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH101" s="1"/>
       <c r="AI101" s="1"/>
       <c r="AJ101" s="1"/>
@@ -12199,7 +12491,7 @@
         <v>14.6</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L112" si="26">E102-K102</f>
+        <f t="shared" ref="L102:L112" si="28">E102-K102</f>
         <v>2.9770000000000021</v>
       </c>
       <c r="M102" s="1"/>
@@ -12208,7 +12500,7 @@
         <v>0</v>
       </c>
       <c r="P102" s="1">
-        <f t="shared" ref="P102:P112" si="27">E102/5</f>
+        <f t="shared" ref="P102:P112" si="29">E102/5</f>
         <v>3.5154000000000005</v>
       </c>
       <c r="Q102" s="5">
@@ -12216,15 +12508,15 @@
         <v>27.949400000000004</v>
       </c>
       <c r="R102" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>28</v>
       </c>
       <c r="S102" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11.014393810092733</v>
       </c>
       <c r="T102" s="1">
-        <f t="shared" ref="T102:T112" si="28">(F102+O102)/P102</f>
+        <f t="shared" ref="T102:T112" si="30">(F102+O102)/P102</f>
         <v>3.0494396085793931</v>
       </c>
       <c r="U102" s="1">
@@ -12259,10 +12551,13 @@
       </c>
       <c r="AE102" s="1"/>
       <c r="AF102" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>28</v>
       </c>
-      <c r="AG102" s="1"/>
+      <c r="AG102" s="1">
+        <f t="shared" si="25"/>
+        <v>3.5154000000000005</v>
+      </c>
       <c r="AH102" s="1"/>
       <c r="AI102" s="1"/>
       <c r="AJ102" s="1"/>
@@ -12313,7 +12608,7 @@
         <v>112</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-4</v>
       </c>
       <c r="M103" s="1"/>
@@ -12322,23 +12617,23 @@
         <v>0</v>
       </c>
       <c r="P103" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>21.6</v>
       </c>
       <c r="Q103" s="5">
-        <f t="shared" ref="Q103" si="29">15*P103-O103-F103</f>
+        <f t="shared" ref="Q103" si="31">15*P103-O103-F103</f>
         <v>171</v>
       </c>
       <c r="R103" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>171</v>
       </c>
       <c r="S103" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>14.999999999999998</v>
       </c>
       <c r="T103" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7.083333333333333</v>
       </c>
       <c r="U103" s="1">
@@ -12375,10 +12670,13 @@
         <v>154</v>
       </c>
       <c r="AF103" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>56.43</v>
       </c>
-      <c r="AG103" s="1"/>
+      <c r="AG103" s="1">
+        <f t="shared" si="25"/>
+        <v>7.128000000000001</v>
+      </c>
       <c r="AH103" s="1"/>
       <c r="AI103" s="1"/>
       <c r="AJ103" s="1"/>
@@ -12431,7 +12729,7 @@
         <v>26</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-17</v>
       </c>
       <c r="M104" s="1"/>
@@ -12440,20 +12738,20 @@
         <v>52</v>
       </c>
       <c r="P104" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.8</v>
       </c>
       <c r="Q104" s="5"/>
       <c r="R104" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S104" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>28.333333333333332</v>
       </c>
       <c r="T104" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>28.333333333333332</v>
       </c>
       <c r="U104" s="1">
@@ -12490,10 +12788,13 @@
         <v>155</v>
       </c>
       <c r="AF104" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG104" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG104" s="1">
+        <f t="shared" si="25"/>
+        <v>0.18000000000000002</v>
+      </c>
       <c r="AH104" s="1"/>
       <c r="AI104" s="1"/>
       <c r="AJ104" s="1"/>
@@ -12545,7 +12846,7 @@
         <v>40</v>
       </c>
       <c r="L105" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-37</v>
       </c>
       <c r="M105" s="1"/>
@@ -12554,20 +12855,20 @@
         <v>58</v>
       </c>
       <c r="P105" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.6</v>
       </c>
       <c r="Q105" s="5"/>
       <c r="R105" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S105" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>123.33333333333334</v>
       </c>
       <c r="T105" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>123.33333333333334</v>
       </c>
       <c r="U105" s="1">
@@ -12604,10 +12905,13 @@
         <v>156</v>
       </c>
       <c r="AF105" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG105" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG105" s="1">
+        <f t="shared" si="25"/>
+        <v>0.06</v>
+      </c>
       <c r="AH105" s="1"/>
       <c r="AI105" s="1"/>
       <c r="AJ105" s="1"/>
@@ -12659,7 +12963,7 @@
         <v>271</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-10</v>
       </c>
       <c r="M106" s="1"/>
@@ -12668,7 +12972,7 @@
         <v>83</v>
       </c>
       <c r="P106" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>52.2</v>
       </c>
       <c r="Q106" s="5">
@@ -12676,15 +12980,15 @@
         <v>429.20000000000005</v>
       </c>
       <c r="R106" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>429</v>
       </c>
       <c r="S106" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>10.996168582375478</v>
       </c>
       <c r="T106" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2.7777777777777777</v>
       </c>
       <c r="U106" s="1">
@@ -12721,10 +13025,13 @@
         <v>157</v>
       </c>
       <c r="AF106" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>42.900000000000006</v>
       </c>
-      <c r="AG106" s="1"/>
+      <c r="AG106" s="1">
+        <f t="shared" si="25"/>
+        <v>5.2200000000000006</v>
+      </c>
       <c r="AH106" s="1"/>
       <c r="AI106" s="1"/>
       <c r="AJ106" s="1"/>
@@ -12775,7 +13082,7 @@
         <v>101</v>
       </c>
       <c r="L107" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-65</v>
       </c>
       <c r="M107" s="1"/>
@@ -12784,20 +13091,20 @@
         <v>127</v>
       </c>
       <c r="P107" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>7.2</v>
       </c>
       <c r="Q107" s="5"/>
       <c r="R107" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S107" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>23.888888888888889</v>
       </c>
       <c r="T107" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>23.888888888888889</v>
       </c>
       <c r="U107" s="1">
@@ -12834,10 +13141,13 @@
         <v>159</v>
       </c>
       <c r="AF107" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG107" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG107" s="1">
+        <f t="shared" si="25"/>
+        <v>0.72000000000000008</v>
+      </c>
       <c r="AH107" s="1"/>
       <c r="AI107" s="1"/>
       <c r="AJ107" s="1"/>
@@ -12889,7 +13199,7 @@
         <v>62</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-24</v>
       </c>
       <c r="M108" s="1"/>
@@ -12898,20 +13208,20 @@
         <v>221</v>
       </c>
       <c r="P108" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>7.6</v>
       </c>
       <c r="Q108" s="5"/>
       <c r="R108" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S108" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>24.342105263157897</v>
       </c>
       <c r="T108" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>24.342105263157897</v>
       </c>
       <c r="U108" s="1">
@@ -12948,10 +13258,13 @@
         <v>160</v>
       </c>
       <c r="AF108" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG108" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG108" s="1">
+        <f t="shared" si="25"/>
+        <v>3.04</v>
+      </c>
       <c r="AH108" s="1"/>
       <c r="AI108" s="1"/>
       <c r="AJ108" s="1"/>
@@ -12998,7 +13311,7 @@
         <v>16</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-4</v>
       </c>
       <c r="M109" s="1"/>
@@ -13007,22 +13320,22 @@
         <v>0</v>
       </c>
       <c r="P109" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>2.4</v>
       </c>
       <c r="Q109" s="5">
         <v>20</v>
       </c>
       <c r="R109" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="S109" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>8.3333333333333339</v>
       </c>
       <c r="T109" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="U109" s="1">
@@ -13059,10 +13372,13 @@
         <v>169</v>
       </c>
       <c r="AF109" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2</v>
       </c>
-      <c r="AG109" s="1"/>
+      <c r="AG109" s="1">
+        <f t="shared" si="25"/>
+        <v>0.24</v>
+      </c>
       <c r="AH109" s="1"/>
       <c r="AI109" s="1"/>
       <c r="AJ109" s="1"/>
@@ -13109,7 +13425,7 @@
         <v>7</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-3</v>
       </c>
       <c r="M110" s="1"/>
@@ -13118,22 +13434,22 @@
         <v>0</v>
       </c>
       <c r="P110" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.8</v>
       </c>
       <c r="Q110" s="5">
         <v>10</v>
       </c>
       <c r="R110" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="S110" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11.25</v>
       </c>
       <c r="T110" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-1.25</v>
       </c>
       <c r="U110" s="1">
@@ -13170,10 +13486,13 @@
         <v>168</v>
       </c>
       <c r="AF110" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
-      <c r="AG110" s="1"/>
+      <c r="AG110" s="1">
+        <f t="shared" si="25"/>
+        <v>8.0000000000000016E-2</v>
+      </c>
       <c r="AH110" s="1"/>
       <c r="AI110" s="1"/>
       <c r="AJ110" s="1"/>
@@ -13212,7 +13531,7 @@
       <c r="J111" s="9"/>
       <c r="K111" s="9"/>
       <c r="L111" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M111" s="9"/>
@@ -13221,20 +13540,20 @@
         <v>0</v>
       </c>
       <c r="P111" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Q111" s="11"/>
       <c r="R111" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S111" s="1" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T111" s="9" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U111" s="9">
@@ -13271,10 +13590,13 @@
         <v>88</v>
       </c>
       <c r="AF111" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG111" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG111" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH111" s="1"/>
       <c r="AI111" s="1"/>
       <c r="AJ111" s="1"/>
@@ -13319,7 +13641,7 @@
       </c>
       <c r="K112" s="9"/>
       <c r="L112" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M112" s="9"/>
@@ -13328,20 +13650,20 @@
         <v>0</v>
       </c>
       <c r="P112" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Q112" s="11"/>
       <c r="R112" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S112" s="1" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T112" s="9" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U112" s="9">
@@ -13376,10 +13698,13 @@
       </c>
       <c r="AE112" s="9"/>
       <c r="AF112" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AG112" s="1"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG112" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AH112" s="1"/>
       <c r="AI112" s="1"/>
       <c r="AJ112" s="1"/>
